--- a/AAII_Financials/Yearly/MBUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MBUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>MBUMY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -801,8 +801,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>11600</v>
       </c>
       <c r="E12" s="3">
         <v>12400</v>
@@ -856,7 +856,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>55500</v>
+        <v>40800</v>
       </c>
       <c r="E14" s="3">
         <v>-17000</v>
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1600</v>
+        <v>19600</v>
       </c>
       <c r="E15" s="3">
         <v>18100</v>
@@ -987,7 +987,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-51300</v>
+        <v>-36500</v>
       </c>
       <c r="E20" s="3">
         <v>-48900</v>
@@ -1014,7 +1014,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>189000</v>
+        <v>192200</v>
       </c>
       <c r="E21" s="3">
         <v>175900</v>
@@ -1311,7 +1311,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>51300</v>
+        <v>36500</v>
       </c>
       <c r="E32" s="3">
         <v>48900</v>
@@ -1477,7 +1477,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>830500</v>
+        <v>858300</v>
       </c>
       <c r="E41" s="3">
         <v>827200</v>
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>27800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>91500</v>
+        <v>92000</v>
       </c>
       <c r="E47" s="3">
         <v>87600</v>
@@ -1774,7 +1774,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2032900</v>
+        <v>2033000</v>
       </c>
       <c r="E76" s="3">
         <v>2163900</v>
@@ -2829,7 +2829,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
